--- a/docs/attendee-template.xlsx
+++ b/docs/attendee-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\agent\천안시AI문서꾸러미(새롭게)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AC4A67-D9DE-413F-9AAE-0B71E3FDFE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46830154-789D-40F0-BC78-35DBD462E22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F9EC598-0279-4A49-A234-522BA3D21A28}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>기 관</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,102 +50,6 @@
   <si>
     <t>비 고</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국립공주대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나사렛대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남서울대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-  </si>
-  <si>
-    <t>단국대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-  </si>
-  <si>
-    <t>백석대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백석문화대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상명대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선문대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>순천향대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연암대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-  </si>
-  <si>
-    <t>한국기술교육대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호서대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>○ ○ ○</t>
   </si>
 </sst>
 </file>
@@ -586,147 +490,75 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="A7" s="5"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="2"/>
     </row>
   </sheetData>
